--- a/光伏配储项目/电价数据/2026/瑞联站.xlsx
+++ b/光伏配储项目/电价数据/2026/瑞联站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.35287</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8431000000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40885</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33897</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33916</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26532</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.39914</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.08147</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17937</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26058</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26505</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24988</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.60039</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.73145</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.45047</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60588</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.58938</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7584099999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.18965</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.60992</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43926</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44672</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67976</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.9327799999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5327999999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.25573</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39042</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.14431</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.1678</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.36627</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.4811</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.48101</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.74246</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7978999999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.25386</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.03036</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.93487</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.82602</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.78853</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.53107</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.50045</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.48193</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43795</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.74893</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.9298999999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.00334</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52066</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.53814</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.52919</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5293099999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50984</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.24341</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.20931</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.25415</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.48003</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.51383</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5189600000000001</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.70748</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.67944</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.89597</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.4233</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.8019500000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.45535</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.40865</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.69575</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.42369</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.98324</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62659</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8075800000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.86711</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.23775</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.66197</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18682</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.90498</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.28105</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.17013</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.35337</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.09268</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.15472</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.69584</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04299</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9448200000000001</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.03436</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.90795</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.15434</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.95473</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45882</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.9110199999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9559500000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43525</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33587</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5293600000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50668</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.51122</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42585</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39854</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39242</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.44384</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.46183</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34617</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.49383</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.45353</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.11465</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.15483</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26726</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.07237</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.9388099999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.74912</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7340399999999999</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.9420499999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.9351499999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.91354</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.91731</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.19821</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.91492</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.8903300000000001</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.87917</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.0417</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.55735</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.62575</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.82728</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.83978</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.70639</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7569400000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5376000000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.90138</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51852</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52795</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.60463</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.65362</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6683300000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.6775800000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.35772</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.63609</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69512</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47355</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50963</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.6627999999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.8209500000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.8065599999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.94296</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.47741</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6801</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.45564</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.53951</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.63927</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.84276</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5917100000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.9667</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.77079</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.63739</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.59062</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7297899999999999</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4645899999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34344</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.53869</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5178200000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45553</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39648</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46655</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39476</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39806</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38304</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44357</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43724</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6515299999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.45076</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.67811</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42684</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6501699999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31655</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.56253</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.44203</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.50927</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.6948300000000001</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.48998</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.53775</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47912</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6077899999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.7141799999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.5172899999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65355</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5534600000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.52389</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50283</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.47315</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.44846</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.43028</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33985</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28604</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14116</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.45363</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.45754</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.45517</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.43148</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.25985</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.12811</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.47359</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.15106</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26338</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36166</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41553</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31181</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.20795</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.21898</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.20948</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.16885</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.13568</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.23163</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.15661</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.23511</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.19558</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.17192</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.15038</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.23478</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.25784</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.17858</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.25928</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10016</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009460000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20514</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04873</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27384</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20822</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.7180299999999999</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00495</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05928</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05749</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31262</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.35894</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46635</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7863</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87018</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.64437</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.56864</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49313</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44992</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4559</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37673</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.43737</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.55614</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.59854</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.90823</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.48121</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.41711</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.58294</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8563500000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26032</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.6143500000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25474</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25352</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.25155</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27403</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.28623</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.31872</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9057000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.28551</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.6044299999999999</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.48969</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.43918</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.59888</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.21196</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.20399</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.45563</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44989</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.27817</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.22493</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8854500000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.60552</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.24237</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.73412</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8546699999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68311</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.19321</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.20639</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.46446</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5213300000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.38559</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.42919</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.44199</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.27164</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38477</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.27842</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.28005</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.47896</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.15149</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.41015</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30267</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15282</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28178</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01749</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30061</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.27373</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.27882</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.44164</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.56029</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.27125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.26086</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.25857</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.25319</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.24788</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.14346</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.17219</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.16443</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.16489</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.16193</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.13162</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.23041</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.25275</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.25028</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.29897</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.13834</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.17944</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.15455</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.19184</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.17317</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.15687</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.26586</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.26952</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.13669</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.7393200000000001</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.13525</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.6341100000000001</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.4031</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.41633</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26712</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27469</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.43398</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.42415</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.41586</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.28288</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.26494</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27229</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.27978</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.28397</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27282</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.27741</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.27855</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.41332</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27227</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.27491</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.2334</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27045</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.27596</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29363</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.28681</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.27737</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29799</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29471</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.79088</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.45813</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27919</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.26888</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.28909</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45776</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.29651</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.26358</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.28248</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.27389</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28165</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.28584</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.28674</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.27408</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.3031</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.29573</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.19606</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42242</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.70536</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50791</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.47751</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.51403</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5760299999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27474</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.73322</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.46529</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.56145</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.6649299999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.48123</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71175</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.20843</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47706</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22497</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.26269</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.27367</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.18728</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27428</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.26906</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.26847</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.26427</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.17405</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.16724</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.26477</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.2651</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26534</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.26514</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29024</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.1248</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22088</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25143</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.16613</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.17203</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.20425</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.17736</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.13591</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.12851</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.19373</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.22225</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.28322</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.28767</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24962</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.28744</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.26563</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.2184</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.29085</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.22869</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.25246</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27401</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27173</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.26725</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.27292</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.21016</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.26104</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.19635</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.14339</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.21507</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31477</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.26917</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26299</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.26864</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.27365</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26181</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.27545</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.27967</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27034</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.26498</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27317</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28483</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.26428</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6339199999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.48426</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.17699</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.28865</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.42887</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.4101</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.48623</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.43026</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48116</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.66612</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.62226</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6686599999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8268</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5042099999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41195</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.44798</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.29941</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.30654</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.30508</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.29615</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.26832</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.27716</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.25363</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.25095</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.27675</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44047</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.40999</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48916</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.52925</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5628500000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40392</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42357</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67376</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.82863</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.65366</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.45137</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37367</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.4963</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.5797599999999999</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.28509</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.25816</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.23103</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.25177</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.2844100000000001</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75298</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.59989</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.29327</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.29002</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.30616</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38118</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.23434</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.27186</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.25954</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.27091</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2571</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.26481</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.27878</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4192</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.42601</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.43645</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.39599</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41964</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.45179</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.59485</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.5083</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32401</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.20756</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38253</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.20934</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.20421</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.22811</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.26477</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.25947</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.21809</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.26066</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.27372</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.15733</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.15472</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.16965</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.16251</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.19983</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.16834</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.2549</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.25084</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.20554</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.19389</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.13561</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.13591</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.17517</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.13465</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.12673</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.13055</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.17138</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.12859</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.13322</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.13554</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.1587</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.1203</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.85362</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.45483</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>1.46522</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.40843</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00674</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.46379</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.49496</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.47577</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.39214</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.27807</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.23066</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.25497</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.24735</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.25924</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.25467</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.19287</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.22211</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.20142</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.22269</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.25191</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28184</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.24112</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.23519</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.14712</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.15357</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.24093</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.13785</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.14012</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.22136</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.21294</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.27611</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27202</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.26862</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27183</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26151</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.00915</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.16072</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.15809</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.25933</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.21001</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20089</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18118</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.15657</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.04405</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24035</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.00555</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.01085</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15971</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02213</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01373</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04311</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00363</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27987</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.0355</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.00859</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0351</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20936</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27044</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27573</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30175</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25775</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.25757</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28388</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25932</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.14165</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.13822</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.14215</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13985</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.13633</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.12659</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.16353</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21194</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85382</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86324</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28412</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.6533099999999999</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00296</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00214</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47587</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.58584</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50484</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7543800000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.97129</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.59941</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83009</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8283200000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83272</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9334600000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.29779</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.29392</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.27367</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.47129</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.24889</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.24502</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.16154</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.23905</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23313</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.19662</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.22052</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18088</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.17683</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.13576</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.13816</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.12491</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.15359</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.20811</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.28627</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.21926</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.22709</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29361</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24034</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26586</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.26953</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31105</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.24438</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28145</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28643</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4343399999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46188</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48008</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.09356999999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.83563</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.8217100000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54561</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.6662</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.88387</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.55504</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41778</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19349</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.30881</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34146</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29777</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28329</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.52374</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5251399999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.11861</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.83682</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5542</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.72199</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.58331</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.51762</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.69782</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.64673</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.07397</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.85549</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.72961</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58758</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31346</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27448</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.2829700000000001</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27374</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.27873</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.26932</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41886</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5211</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1974</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30335</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.48637</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.49127</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5301900000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43006</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.46331</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.56288</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.48319</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31685</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.7014</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.45474</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35708</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.25773</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4772</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.46686</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.45321</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.47803</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38829</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.42637</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.51627</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41992</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44804</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33259</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17619</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14585</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19878</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04863</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12223</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26013</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.1424</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14613</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18648</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22697</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27593</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16163</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20476</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16609</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.57639</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.41635</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.43016</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39871</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.49305</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.45372</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.4768</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.45555</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.46116</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47645</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40782</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38353</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36131</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36457</v>
       </c>
     </row>
   </sheetData>
